--- a/Organizador imposto de renda.xlsx
+++ b/Organizador imposto de renda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56605CBC-8390-444B-98AB-061F073B88B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69B28857-1B02-4AE0-AD89-DC8FB8DB0A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD745BA2-F341-43CC-8315-1313E39BE12A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BD745BA2-F341-43CC-8315-1313E39BE12A}"/>
   </bookViews>
   <sheets>
     <sheet name="Titular" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>NASCIMENTO</t>
   </si>
   <si>
-    <t>TITULO DE ELEITOR</t>
-  </si>
-  <si>
     <t>RUA</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>HOUVE ALTERAÇÕES DA ENTREGA ANTERIOR</t>
   </si>
   <si>
-    <t>DEPENTENTE CÔNJUGE</t>
-  </si>
-  <si>
     <t>RESIDENTE DO EXTERIOR</t>
   </si>
   <si>
@@ -297,6 +291,12 @@
   </si>
   <si>
     <t>Aluguel Recebido</t>
+  </si>
+  <si>
+    <t>DEPENDENTE CÔNJUGE</t>
+  </si>
+  <si>
+    <t>TÍTULO DE ELEITOR</t>
   </si>
 </sst>
 </file>
@@ -305,11 +305,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
-    <numFmt numFmtId="171" formatCode="00000\-000"/>
-    <numFmt numFmtId="173" formatCode="[&lt;=9999999]###\-####;\(##\)\ #####\-####"/>
-    <numFmt numFmtId="175" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="176" formatCode="mmmm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
+    <numFmt numFmtId="165" formatCode="00000\-000"/>
+    <numFmt numFmtId="166" formatCode="[&lt;=9999999]###\-####;\(##\)\ #####\-####"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="mmmm/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -442,52 +442,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -495,26 +477,26 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -522,13 +504,24 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -536,10 +529,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -561,7 +550,7 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
+      <numFmt numFmtId="164" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -588,6 +577,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -3663,17 +3656,13 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{139E11D8-D3F7-46BC-A6E4-70A5FC12E7AE}" name="Tabela2" displayName="Tabela2" ref="C6:E27" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{139E11D8-D3F7-46BC-A6E4-70A5FC12E7AE}" name="Tabela2" displayName="Tabela2" ref="C6:E27" totalsRowShown="0" dataDxfId="3">
   <autoFilter ref="C6:E27" xr:uid="{139E11D8-D3F7-46BC-A6E4-70A5FC12E7AE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BBCB0A3D-7361-45FE-871B-63A9EFF55212}" name="DATA" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{EB3B89CD-95B6-4B8C-A812-250CADBAEE2D}" name="CATEGORIA" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{9D0D4BE1-2141-4028-BC64-2E50578286F3}" name="VALOR" dataDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{BBCB0A3D-7361-45FE-871B-63A9EFF55212}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{EB3B89CD-95B6-4B8C-A812-250CADBAEE2D}" name="CATEGORIA" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9D0D4BE1-2141-4028-BC64-2E50578286F3}" name="VALOR" dataDxfId="0" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4029,88 +4018,88 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="24"/>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C9" s="3" t="s">
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="22"/>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="23"/>
-    </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="18"/>
-    </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="18"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="18"/>
+      <c r="D17" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -4140,127 +4129,127 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="24"/>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="2" t="s">
+      <c r="D6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="7" t="s">
+      <c r="D7" s="18">
+        <v>12312312322</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="18">
+        <v>12312312322</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="3" t="s">
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="18">
+        <v>12312312322</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="24">
-        <v>12312312322</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C9" s="3"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="7" t="s">
+      <c r="D18" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="24">
-        <v>12312312322</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="3"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="7" t="s">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="21" spans="3:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C21" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="24">
-        <v>12312312322</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="3"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="21" spans="3:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C21" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="9">
+      <c r="C22" s="26">
         <f>SUM(D17,D12,D7)</f>
         <v>36936936966</v>
       </c>
-      <c r="D22" s="8"/>
+      <c r="D22" s="27"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -4299,136 +4288,136 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="25">
+      <c r="C7" s="19">
         <v>20</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="28"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="28"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="28"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="28"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="28"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="28"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="28"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="28"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="28"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="28"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="29"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="29"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="29"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="29"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="29"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C23" s="29"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C24" s="29"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C25" s="29"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="27"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C26" s="29"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="27"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C27" s="29"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="27"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="21"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -4467,275 +4456,275 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
